--- a/data/analysis_panns/summary.xlsx
+++ b/data/analysis_panns/summary.xlsx
@@ -465,7 +465,7 @@
         <v>20</v>
       </c>
       <c r="J2">
-        <v>74</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -497,7 +497,7 @@
         <v>20</v>
       </c>
       <c r="J3">
-        <v>93</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -529,7 +529,7 @@
         <v>20</v>
       </c>
       <c r="J4">
-        <v>55</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -561,7 +561,7 @@
         <v>20</v>
       </c>
       <c r="J5">
-        <v>67</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -575,25 +575,25 @@
         <v>1</v>
       </c>
       <c r="D6">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="E6">
-        <v>0.333</v>
+        <v>0.4</v>
       </c>
       <c r="F6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I6">
         <v>20</v>
       </c>
       <c r="J6">
-        <v>34</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -625,7 +625,7 @@
         <v>20</v>
       </c>
       <c r="J7">
-        <v>40</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -657,7 +657,7 @@
         <v>20</v>
       </c>
       <c r="J8">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -689,7 +689,7 @@
         <v>20</v>
       </c>
       <c r="J9">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/data/analysis_panns/summary.xlsx
+++ b/data/analysis_panns/summary.xlsx
@@ -14,7 +14,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="12">
+  <si>
+    <t>audio</t>
+  </si>
   <si>
     <t>window</t>
   </si>
@@ -44,6 +47,9 @@
   </si>
   <si>
     <t>SPI</t>
+  </si>
+  <si>
+    <t>panns</t>
   </si>
 </sst>
 </file>
@@ -401,10 +407,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -435,260 +441,287 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2">
-        <v>1</v>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" t="s">
+        <v>11</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
         <v>0.8</v>
       </c>
-      <c r="D2">
+      <c r="E2">
         <v>0.2</v>
       </c>
-      <c r="E2">
+      <c r="F2">
         <v>0.32</v>
       </c>
-      <c r="F2">
+      <c r="G2">
         <v>4</v>
       </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
       <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
         <v>16</v>
       </c>
-      <c r="I2">
+      <c r="J2">
         <v>20</v>
       </c>
-      <c r="J2">
+      <c r="K2">
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
-      <c r="A3">
-        <v>1</v>
+    <row r="3" spans="1:11">
+      <c r="A3" t="s">
+        <v>11</v>
       </c>
       <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
         <v>0.5</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>0.833</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>0.25</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>0.385</v>
       </c>
-      <c r="F3">
-        <v>5</v>
-      </c>
       <c r="G3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
         <v>15</v>
       </c>
-      <c r="I3">
+      <c r="J3">
         <v>20</v>
       </c>
-      <c r="J3">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4">
-        <v>2.5</v>
+      <c r="K3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" t="s">
+        <v>11</v>
       </c>
       <c r="B4">
         <v>2.5</v>
       </c>
       <c r="C4">
+        <v>2.5</v>
+      </c>
+      <c r="D4">
         <v>0.714</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>0.25</v>
       </c>
-      <c r="E4">
+      <c r="F4">
         <v>0.37</v>
       </c>
-      <c r="F4">
-        <v>5</v>
-      </c>
       <c r="G4">
+        <v>5</v>
+      </c>
+      <c r="H4">
         <v>2</v>
       </c>
-      <c r="H4">
+      <c r="I4">
         <v>15</v>
       </c>
-      <c r="I4">
+      <c r="J4">
         <v>20</v>
       </c>
-      <c r="J4">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5">
+      <c r="K4">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5">
         <v>2.5</v>
       </c>
-      <c r="B5">
+      <c r="C5">
         <v>1.25</v>
       </c>
-      <c r="C5">
+      <c r="D5">
         <v>0.75</v>
       </c>
-      <c r="D5">
+      <c r="E5">
         <v>0.3</v>
       </c>
-      <c r="E5">
+      <c r="F5">
         <v>0.429</v>
       </c>
-      <c r="F5">
+      <c r="G5">
         <v>6</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>2</v>
       </c>
-      <c r="H5">
+      <c r="I5">
         <v>14</v>
       </c>
-      <c r="I5">
+      <c r="J5">
         <v>20</v>
       </c>
-      <c r="J5">
+      <c r="K5">
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
-      <c r="A6">
-        <v>5</v>
+    <row r="6" spans="1:11">
+      <c r="A6" t="s">
+        <v>11</v>
       </c>
       <c r="B6">
         <v>5</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
         <v>0.25</v>
       </c>
-      <c r="E6">
+      <c r="F6">
         <v>0.4</v>
       </c>
-      <c r="F6">
-        <v>5</v>
-      </c>
       <c r="G6">
+        <v>5</v>
+      </c>
+      <c r="H6">
         <v>0</v>
       </c>
-      <c r="H6">
+      <c r="I6">
         <v>15</v>
       </c>
-      <c r="I6">
+      <c r="J6">
         <v>20</v>
       </c>
-      <c r="J6">
+      <c r="K6">
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
-      <c r="A7">
-        <v>5</v>
+    <row r="7" spans="1:11">
+      <c r="A7" t="s">
+        <v>11</v>
       </c>
       <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7">
         <v>2.5</v>
       </c>
-      <c r="C7">
+      <c r="D7">
         <v>0.714</v>
       </c>
-      <c r="D7">
+      <c r="E7">
         <v>0.25</v>
       </c>
-      <c r="E7">
+      <c r="F7">
         <v>0.37</v>
       </c>
-      <c r="F7">
-        <v>5</v>
-      </c>
       <c r="G7">
+        <v>5</v>
+      </c>
+      <c r="H7">
         <v>2</v>
       </c>
-      <c r="H7">
+      <c r="I7">
         <v>15</v>
       </c>
-      <c r="I7">
+      <c r="J7">
         <v>20</v>
       </c>
-      <c r="J7">
+      <c r="K7">
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
-      <c r="A8">
-        <v>10</v>
+    <row r="8" spans="1:11">
+      <c r="A8" t="s">
+        <v>11</v>
       </c>
       <c r="B8">
         <v>10</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
         <v>0.15</v>
       </c>
-      <c r="E8">
+      <c r="F8">
         <v>0.261</v>
       </c>
-      <c r="F8">
+      <c r="G8">
         <v>3</v>
       </c>
-      <c r="G8">
+      <c r="H8">
         <v>0</v>
       </c>
-      <c r="H8">
+      <c r="I8">
         <v>17</v>
       </c>
-      <c r="I8">
+      <c r="J8">
         <v>20</v>
       </c>
-      <c r="J8">
+      <c r="K8">
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
-      <c r="A9">
+    <row r="9" spans="1:11">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9">
         <v>10</v>
       </c>
-      <c r="B9">
-        <v>5</v>
-      </c>
       <c r="C9">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
         <v>0.15</v>
       </c>
-      <c r="E9">
+      <c r="F9">
         <v>0.261</v>
       </c>
-      <c r="F9">
+      <c r="G9">
         <v>3</v>
       </c>
-      <c r="G9">
+      <c r="H9">
         <v>0</v>
       </c>
-      <c r="H9">
+      <c r="I9">
         <v>17</v>
       </c>
-      <c r="I9">
+      <c r="J9">
         <v>20</v>
       </c>
-      <c r="J9">
+      <c r="K9">
         <v>12</v>
       </c>
     </row>

--- a/data/analysis_panns/summary.xlsx
+++ b/data/analysis_panns/summary.xlsx
@@ -46,7 +46,7 @@
     <t>support</t>
   </si>
   <si>
-    <t>SPI</t>
+    <t>API</t>
   </si>
   <si>
     <t>panns</t>
@@ -512,7 +512,7 @@
         <v>20</v>
       </c>
       <c r="K3">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -547,7 +547,7 @@
         <v>20</v>
       </c>
       <c r="K4">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -561,22 +561,22 @@
         <v>1.25</v>
       </c>
       <c r="D5">
-        <v>0.75</v>
+        <v>0.714</v>
       </c>
       <c r="E5">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="F5">
-        <v>0.429</v>
+        <v>0.37</v>
       </c>
       <c r="G5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H5">
         <v>2</v>
       </c>
       <c r="I5">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J5">
         <v>20</v>
